--- a/log_resuts.xlsx
+++ b/log_resuts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,57 @@
         <v>0.8953185955786735</v>
       </c>
       <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:57:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>distilbert-base-uncased</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>q_lin,v_lin</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2244.61</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3796542286872864</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9040962288686606</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/log_resuts.xlsx
+++ b/log_resuts.xlsx
@@ -1,37 +1,117 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A453784\Simplon\M1B1_classification_auto\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FBE9D3-2A8F-45D5-A61C-B2836438FAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>model_name</t>
+  </si>
+  <si>
+    <t>max_length</t>
+  </si>
+  <si>
+    <t>lora_r</t>
+  </si>
+  <si>
+    <t>lora_alpha</t>
+  </si>
+  <si>
+    <t>lora_dropout</t>
+  </si>
+  <si>
+    <t>lora_targets</t>
+  </si>
+  <si>
+    <t>learning_rate</t>
+  </si>
+  <si>
+    <t>batch_train</t>
+  </si>
+  <si>
+    <t>batch_eval</t>
+  </si>
+  <si>
+    <t>epochs</t>
+  </si>
+  <si>
+    <t>training_time_sec</t>
+  </si>
+  <si>
+    <t>eval_loss</t>
+  </si>
+  <si>
+    <t>eval_accuracy</t>
+  </si>
+  <si>
+    <t>eval_f1_weighted</t>
+  </si>
+  <si>
+    <t>eval_f1_macro</t>
+  </si>
+  <si>
+    <t>distilbert-base-uncased</t>
+  </si>
+  <si>
+    <t>q_lin,v_lin</t>
+  </si>
+  <si>
+    <t>2026-06-08 19:40:49</t>
+  </si>
+  <si>
+    <t>2026-06-08 20:29:57</t>
+  </si>
+  <si>
+    <t>2026-06-08 21:30:57</t>
+  </si>
+  <si>
+    <t>2026-06-08 22:27:11</t>
+  </si>
+  <si>
+    <t>q_lin,k_lin,v_lin</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +126,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,192 +450,259 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>model_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>max_length</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>lora_r</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>lora_alpha</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>lora_dropout</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>lora_targets</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>learning_rate</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>batch_train</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>batch_eval</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>epochs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>training_time_sec</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>eval_loss</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>eval_accuracy</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>eval_f1</t>
-        </is>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-07 13:36:36</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>distilbert-base-uncased</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
         <v>48</v>
       </c>
-      <c r="D2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
         <v>16</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>q_lin,v_lin</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="F2">
+        <v>0.05</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
         <v>3</v>
       </c>
-      <c r="L2" t="n">
-        <v>2224.69</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.3858035504817963</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.8953185955786735</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="L2">
+        <v>2470.13</v>
+      </c>
+      <c r="M2">
+        <v>1.0714080333709719</v>
+      </c>
+      <c r="N2">
+        <v>0.75162548764629389</v>
+      </c>
+      <c r="O2">
+        <v>0.73489630511840054</v>
+      </c>
+      <c r="P2">
+        <v>0.73487236919702226</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-07 22:57:41</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>distilbert-base-uncased</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
         <v>48</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
         <v>16</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3">
+        <v>0.05</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2219.21</v>
+      </c>
+      <c r="M3">
+        <v>0.38904336094856262</v>
+      </c>
+      <c r="N3">
+        <v>0.88979193758127439</v>
+      </c>
+      <c r="O3">
+        <v>0.88946578096489592</v>
+      </c>
+      <c r="P3">
+        <v>0.88941127830874744</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>48</v>
+      </c>
+      <c r="D4">
+        <v>16</v>
+      </c>
+      <c r="E4">
         <v>32</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4">
         <v>0.05</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>q_lin,v_lin</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>8</v>
+      </c>
+      <c r="K4">
         <v>3</v>
       </c>
-      <c r="L3" t="n">
-        <v>2244.61</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.3796542286872864</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.9040962288686606</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="L4">
+        <v>2507.88</v>
+      </c>
+      <c r="M4">
+        <v>0.37404376268386841</v>
+      </c>
+      <c r="N4">
+        <v>0.89759427828348504</v>
+      </c>
+      <c r="O4">
+        <v>0.89765497206268885</v>
+      </c>
+      <c r="P4">
+        <v>0.89761229077001881</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>48</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>0.05</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2695.07</v>
+      </c>
+      <c r="M5">
+        <v>0.37338021397590643</v>
+      </c>
+      <c r="N5">
+        <v>0.89596879063719115</v>
+      </c>
+      <c r="O5">
+        <v>0.89584474593630992</v>
+      </c>
+      <c r="P5">
+        <v>0.89581982425621665</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
